--- a/HGAMD生産計画 2026.10.10.xlsx
+++ b/HGAMD生産計画 2026.10.10.xlsx
@@ -7,7 +7,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'JIT日一覧'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'JIT日一覧'!A1:G87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'JIT日一覧'!A1:H87</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -431,7 +431,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:H87"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -440,6 +440,7 @@
     <col min="5" max="5" width="13.83203125" customWidth="1"/>
     <col min="6" max="6" width="51.83203125" customWidth="1"/>
     <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,6 +465,9 @@
       <c r="G1" t="str" s="3">
         <v>JIT日</v>
       </c>
+      <c r="H1" t="str" s="3">
+        <v>備考</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str" s="2">
@@ -487,6 +491,9 @@
       <c r="G2" s="4" t="d">
         <v>2026-07-11T00:00:00.000Z</v>
       </c>
+      <c r="H2" t="str" s="2">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str" s="2">
@@ -510,6 +517,9 @@
       <c r="G3" s="4" t="d">
         <v>2026-07-14T00:00:00.000Z</v>
       </c>
+      <c r="H3" t="str" s="2">
+        <v>B&amp;R</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str" s="2">
@@ -533,6 +543,9 @@
       <c r="G4" s="4" t="d">
         <v>2026-07-17T00:00:00.000Z</v>
       </c>
+      <c r="H4" t="str" s="2">
+        <v>ATC</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str" s="2">
@@ -556,6 +569,9 @@
       <c r="G5" s="4" t="d">
         <v>2026-07-24T00:00:00.000Z</v>
       </c>
+      <c r="H5" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str" s="2">
@@ -579,6 +595,9 @@
       <c r="G6" s="4" t="d">
         <v>2026-07-24T00:00:00.000Z</v>
       </c>
+      <c r="H6" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str" s="2">
@@ -602,6 +621,9 @@
       <c r="G7" s="4" t="d">
         <v>2026-07-31T00:00:00.000Z</v>
       </c>
+      <c r="H7" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str" s="2">
@@ -625,6 +647,9 @@
       <c r="G8" s="4" t="d">
         <v>2026-07-31T00:00:00.000Z</v>
       </c>
+      <c r="H8" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str" s="2">
@@ -648,6 +673,9 @@
       <c r="G9" s="4" t="d">
         <v>2026-08-01T00:00:00.000Z</v>
       </c>
+      <c r="H9" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str" s="2">
@@ -671,6 +699,9 @@
       <c r="G10" s="4" t="d">
         <v>2026-08-07T00:00:00.000Z</v>
       </c>
+      <c r="H10" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str" s="2">
@@ -694,6 +725,9 @@
       <c r="G11" s="4" t="d">
         <v>2026-08-07T00:00:00.000Z</v>
       </c>
+      <c r="H11" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str" s="2">
@@ -717,6 +751,9 @@
       <c r="G12" s="4" t="d">
         <v>2026-08-20T00:00:00.000Z</v>
       </c>
+      <c r="H12" t="str" s="2">
+        <v>ARM</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str" s="2">
@@ -740,6 +777,9 @@
       <c r="G13" s="4" t="d">
         <v>2026-08-20T00:00:00.000Z</v>
       </c>
+      <c r="H13" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str" s="2">
@@ -763,6 +803,9 @@
       <c r="G14" s="4" t="d">
         <v>2026-08-25T00:00:00.000Z</v>
       </c>
+      <c r="H14" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str" s="2">
@@ -786,6 +829,9 @@
       <c r="G15" s="4" t="d">
         <v>2026-08-25T00:00:00.000Z</v>
       </c>
+      <c r="H15" t="str" s="2">
+        <v>ATC</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str" s="2">
@@ -809,6 +855,9 @@
       <c r="G16" s="4" t="d">
         <v>2026-08-28T00:00:00.000Z</v>
       </c>
+      <c r="H16" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str" s="2">
@@ -832,6 +881,9 @@
       <c r="G17" s="4" t="d">
         <v>2026-08-28T00:00:00.000Z</v>
       </c>
+      <c r="H17" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str" s="2">
@@ -855,6 +907,9 @@
       <c r="G18" s="4" t="d">
         <v>2026-09-02T00:00:00.000Z</v>
       </c>
+      <c r="H18" t="str" s="2">
+        <v>ATC</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str" s="2">
@@ -878,6 +933,9 @@
       <c r="G19" s="4" t="d">
         <v>2026-09-02T00:00:00.000Z</v>
       </c>
+      <c r="H19" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str" s="2">
@@ -901,6 +959,9 @@
       <c r="G20" s="4" t="d">
         <v>2026-09-04T00:00:00.000Z</v>
       </c>
+      <c r="H20" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str" s="2">
@@ -924,6 +985,9 @@
       <c r="G21" s="4" t="d">
         <v>2026-09-04T00:00:00.000Z</v>
       </c>
+      <c r="H21" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str" s="2">
@@ -947,6 +1011,9 @@
       <c r="G22" s="4" t="d">
         <v>2026-09-08T00:00:00.000Z</v>
       </c>
+      <c r="H22" t="str" s="2">
+        <v>ARM</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str" s="2">
@@ -970,6 +1037,9 @@
       <c r="G23" s="4" t="d">
         <v>2026-09-11T00:00:00.000Z</v>
       </c>
+      <c r="H23" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str" s="2">
@@ -993,6 +1063,9 @@
       <c r="G24" s="4" t="d">
         <v>2026-09-11T00:00:00.000Z</v>
       </c>
+      <c r="H24" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str" s="2">
@@ -1016,6 +1089,9 @@
       <c r="G25" s="4" t="d">
         <v>2026-09-12T00:00:00.000Z</v>
       </c>
+      <c r="H25" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str" s="2">
@@ -1039,6 +1115,9 @@
       <c r="G26" s="4" t="d">
         <v>2026-09-15T00:00:00.000Z</v>
       </c>
+      <c r="H26" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str" s="2">
@@ -1062,6 +1141,9 @@
       <c r="G27" s="4" t="d">
         <v>2026-09-15T00:00:00.000Z</v>
       </c>
+      <c r="H27" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str" s="2">
@@ -1085,6 +1167,9 @@
       <c r="G28" s="4" t="d">
         <v>2026-09-25T00:00:00.000Z</v>
       </c>
+      <c r="H28" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str" s="2">
@@ -1108,6 +1193,9 @@
       <c r="G29" s="4" t="d">
         <v>2026-09-30T00:00:00.000Z</v>
       </c>
+      <c r="H29" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str" s="2">
@@ -1131,6 +1219,9 @@
       <c r="G30" s="4" t="d">
         <v>2026-09-30T00:00:00.000Z</v>
       </c>
+      <c r="H30" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str" s="2">
@@ -1154,6 +1245,9 @@
       <c r="G31" s="4" t="d">
         <v>2026-10-02T00:00:00.000Z</v>
       </c>
+      <c r="H31" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str" s="2">
@@ -1177,6 +1271,9 @@
       <c r="G32" s="4" t="d">
         <v>2026-10-02T00:00:00.000Z</v>
       </c>
+      <c r="H32" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str" s="2">
@@ -1200,6 +1297,9 @@
       <c r="G33" s="4" t="d">
         <v>2026-10-10T00:00:00.000Z</v>
       </c>
+      <c r="H33" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str" s="2">
@@ -1223,6 +1323,9 @@
       <c r="G34" s="4" t="d">
         <v>2026-10-10T00:00:00.000Z</v>
       </c>
+      <c r="H34" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str" s="2">
@@ -1246,6 +1349,9 @@
       <c r="G35" s="4" t="d">
         <v>2026-10-14T00:00:00.000Z</v>
       </c>
+      <c r="H35" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str" s="2">
@@ -1269,6 +1375,9 @@
       <c r="G36" s="4" t="d">
         <v>2026-10-14T00:00:00.000Z</v>
       </c>
+      <c r="H36" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str" s="2">
@@ -1292,6 +1401,9 @@
       <c r="G37" s="4" t="d">
         <v>2026-10-23T00:00:00.000Z</v>
       </c>
+      <c r="H37" t="str" s="2">
+        <v>ARM</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str" s="2">
@@ -1315,6 +1427,9 @@
       <c r="G38" s="4" t="d">
         <v>2026-10-23T00:00:00.000Z</v>
       </c>
+      <c r="H38" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str" s="2">
@@ -1338,6 +1453,9 @@
       <c r="G39" s="4" t="d">
         <v>2026-10-28T00:00:00.000Z</v>
       </c>
+      <c r="H39" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str" s="2">
@@ -1361,6 +1479,9 @@
       <c r="G40" s="4" t="d">
         <v>2026-10-28T00:00:00.000Z</v>
       </c>
+      <c r="H40" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str" s="2">
@@ -1384,6 +1505,9 @@
       <c r="G41" s="4" t="d">
         <v>2026-10-30T00:00:00.000Z</v>
       </c>
+      <c r="H41" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str" s="2">
@@ -1407,6 +1531,9 @@
       <c r="G42" s="4" t="d">
         <v>2026-10-30T00:00:00.000Z</v>
       </c>
+      <c r="H42" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str" s="2">
@@ -1430,6 +1557,9 @@
       <c r="G43" s="4" t="d">
         <v>2026-11-04T00:00:00.000Z</v>
       </c>
+      <c r="H43" t="str" s="2">
+        <v>ATC</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str" s="2">
@@ -1453,6 +1583,9 @@
       <c r="G44" s="4" t="d">
         <v>2026-11-04T00:00:00.000Z</v>
       </c>
+      <c r="H44" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str" s="2">
@@ -1476,6 +1609,9 @@
       <c r="G45" s="4" t="d">
         <v>2026-11-10T00:00:00.000Z</v>
       </c>
+      <c r="H45" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str" s="2">
@@ -1499,6 +1635,9 @@
       <c r="G46" s="4" t="d">
         <v>2026-11-10T00:00:00.000Z</v>
       </c>
+      <c r="H46" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str" s="2">
@@ -1522,6 +1661,9 @@
       <c r="G47" s="4" t="d">
         <v>2026-11-13T00:00:00.000Z</v>
       </c>
+      <c r="H47" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str" s="2">
@@ -1545,6 +1687,9 @@
       <c r="G48" s="4" t="d">
         <v>2026-11-13T00:00:00.000Z</v>
       </c>
+      <c r="H48" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str" s="2">
@@ -1568,6 +1713,9 @@
       <c r="G49" s="4" t="d">
         <v>2026-11-19T00:00:00.000Z</v>
       </c>
+      <c r="H49" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str" s="2">
@@ -1591,6 +1739,9 @@
       <c r="G50" s="4" t="d">
         <v>2026-11-19T00:00:00.000Z</v>
       </c>
+      <c r="H50" t="str" s="2">
+        <v>ATC</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str" s="2">
@@ -1614,6 +1765,9 @@
       <c r="G51" s="4" t="d">
         <v>2026-11-24T00:00:00.000Z</v>
       </c>
+      <c r="H51" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str" s="2">
@@ -1637,6 +1791,9 @@
       <c r="G52" s="4" t="d">
         <v>2026-11-24T00:00:00.000Z</v>
       </c>
+      <c r="H52" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str" s="2">
@@ -1660,6 +1817,9 @@
       <c r="G53" s="4" t="d">
         <v>2026-11-27T00:00:00.000Z</v>
       </c>
+      <c r="H53" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str" s="2">
@@ -1683,6 +1843,9 @@
       <c r="G54" s="4" t="d">
         <v>2026-11-27T00:00:00.000Z</v>
       </c>
+      <c r="H54" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str" s="2">
@@ -1706,6 +1869,9 @@
       <c r="G55" s="4" t="d">
         <v>2026-12-02T00:00:00.000Z</v>
       </c>
+      <c r="H55" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str" s="2">
@@ -1729,6 +1895,9 @@
       <c r="G56" s="4" t="d">
         <v>2026-12-02T00:00:00.000Z</v>
       </c>
+      <c r="H56" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str" s="2">
@@ -1752,6 +1921,9 @@
       <c r="G57" s="4" t="d">
         <v>2026-12-05T00:00:00.000Z</v>
       </c>
+      <c r="H57" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str" s="2">
@@ -1775,6 +1947,9 @@
       <c r="G58" s="4" t="d">
         <v>2026-12-05T00:00:00.000Z</v>
       </c>
+      <c r="H58" t="str" s="2">
+        <v>ATC</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str" s="2">
@@ -1798,6 +1973,9 @@
       <c r="G59" s="4" t="d">
         <v>2026-12-09T00:00:00.000Z</v>
       </c>
+      <c r="H59" t="str" s="2">
+        <v>ATC</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str" s="2">
@@ -1821,6 +1999,9 @@
       <c r="G60" s="4" t="d">
         <v>2026-12-10T00:00:00.000Z</v>
       </c>
+      <c r="H60" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str" s="2">
@@ -1844,6 +2025,9 @@
       <c r="G61" s="4" t="d">
         <v>2026-12-10T00:00:00.000Z</v>
       </c>
+      <c r="H61" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str" s="2">
@@ -1867,6 +2051,9 @@
       <c r="G62" s="4" t="d">
         <v>2026-12-12T00:00:00.000Z</v>
       </c>
+      <c r="H62" t="str" s="2">
+        <v>ATC</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str" s="2">
@@ -1890,6 +2077,9 @@
       <c r="G63" s="4" t="d">
         <v>2026-12-15T00:00:00.000Z</v>
       </c>
+      <c r="H63" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str" s="2">
@@ -1913,6 +2103,9 @@
       <c r="G64" s="4" t="d">
         <v>2026-12-16T00:00:00.000Z</v>
       </c>
+      <c r="H64" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str" s="2">
@@ -1936,6 +2129,9 @@
       <c r="G65" s="4" t="d">
         <v>2026-12-18T00:00:00.000Z</v>
       </c>
+      <c r="H65" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str" s="2">
@@ -1959,6 +2155,9 @@
       <c r="G66" s="4" t="d">
         <v>2026-12-22T00:00:00.000Z</v>
       </c>
+      <c r="H66" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str" s="2">
@@ -1982,6 +2181,9 @@
       <c r="G67" s="4" t="d">
         <v>2026-12-24T00:00:00.000Z</v>
       </c>
+      <c r="H67" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str" s="2">
@@ -2005,6 +2207,9 @@
       <c r="G68" s="4" t="d">
         <v>2026-12-26T00:00:00.000Z</v>
       </c>
+      <c r="H68" t="str" s="2">
+        <v>ATC</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str" s="2">
@@ -2028,6 +2233,9 @@
       <c r="G69" s="4" t="d">
         <v>2027-01-05T00:00:00.000Z</v>
       </c>
+      <c r="H69" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str" s="2">
@@ -2051,6 +2259,9 @@
       <c r="G70" s="4" t="d">
         <v>2027-01-07T00:00:00.000Z</v>
       </c>
+      <c r="H70" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str" s="2">
@@ -2074,6 +2285,9 @@
       <c r="G71" s="4" t="d">
         <v>2027-01-09T00:00:00.000Z</v>
       </c>
+      <c r="H71" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str" s="2">
@@ -2097,6 +2311,9 @@
       <c r="G72" s="4" t="d">
         <v>2027-01-13T00:00:00.000Z</v>
       </c>
+      <c r="H72" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str" s="2">
@@ -2120,6 +2337,9 @@
       <c r="G73" s="4" t="d">
         <v>2027-01-13T00:00:00.000Z</v>
       </c>
+      <c r="H73" t="str" s="2">
+        <v>ATC</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str" s="2">
@@ -2143,6 +2363,9 @@
       <c r="G74" s="4" t="d">
         <v>2027-01-15T00:00:00.000Z</v>
       </c>
+      <c r="H74" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str" s="2">
@@ -2166,6 +2389,9 @@
       <c r="G75" s="4" t="d">
         <v>2027-01-15T00:00:00.000Z</v>
       </c>
+      <c r="H75" t="str" s="2">
+        <v>ATC</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str" s="2">
@@ -2189,6 +2415,9 @@
       <c r="G76" s="4" t="d">
         <v>2027-01-19T00:00:00.000Z</v>
       </c>
+      <c r="H76" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str" s="2">
@@ -2212,6 +2441,9 @@
       <c r="G77" s="4" t="d">
         <v>2027-01-20T00:00:00.000Z</v>
       </c>
+      <c r="H77" t="str" s="2">
+        <v>ATC</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str" s="2">
@@ -2235,6 +2467,9 @@
       <c r="G78" s="4" t="d">
         <v>2027-01-22T00:00:00.000Z</v>
       </c>
+      <c r="H78" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str" s="2">
@@ -2258,6 +2493,9 @@
       <c r="G79" s="4" t="d">
         <v>2027-01-23T00:00:00.000Z</v>
       </c>
+      <c r="H79" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str" s="2">
@@ -2281,6 +2519,9 @@
       <c r="G80" s="4" t="d">
         <v>2027-01-27T00:00:00.000Z</v>
       </c>
+      <c r="H80" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str" s="2">
@@ -2304,6 +2545,9 @@
       <c r="G81" s="4" t="d">
         <v>2027-01-29T00:00:00.000Z</v>
       </c>
+      <c r="H81" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str" s="2">
@@ -2327,6 +2571,9 @@
       <c r="G82" s="4" t="d">
         <v>2027-02-02T00:00:00.000Z</v>
       </c>
+      <c r="H82" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str" s="2">
@@ -2350,6 +2597,9 @@
       <c r="G83" s="4" t="d">
         <v>2027-02-03T00:00:00.000Z</v>
       </c>
+      <c r="H83" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str" s="2">
@@ -2373,6 +2623,9 @@
       <c r="G84" s="4" t="d">
         <v>2027-02-05T00:00:00.000Z</v>
       </c>
+      <c r="H84" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str" s="2">
@@ -2396,6 +2649,9 @@
       <c r="G85" s="4" t="d">
         <v>2027-02-09T00:00:00.000Z</v>
       </c>
+      <c r="H85" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str" s="2">
@@ -2419,6 +2675,9 @@
       <c r="G86" s="4" t="d">
         <v>2027-02-12T00:00:00.000Z</v>
       </c>
+      <c r="H86" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str" s="2">
@@ -2442,16 +2701,19 @@
       <c r="G87" s="4" t="d">
         <v>2027-02-13T00:00:00.000Z</v>
       </c>
+      <c r="H87" t="str" s="2">
+        <v>Y化 Σ10</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G87"/>
+  <autoFilter ref="A1:H87"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P / &amp;N</oddFooter>
   </headerFooter>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H87"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/HGAMD生産計画 2026.10.10.xlsx
+++ b/HGAMD生産計画 2026.10.10.xlsx
@@ -492,7 +492,7 @@
         <v>2026-07-11T00:00:00.000Z</v>
       </c>
       <c r="H2" t="str" s="2">
-        <v/>
+        <v>Y化 Σ7</v>
       </c>
     </row>
     <row r="3">
